--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.39529419957392</v>
+        <v>6.726735307430762</v>
       </c>
       <c r="D2" t="n">
-        <v>41.34831598402591</v>
+        <v>6.719101347404211</v>
       </c>
       <c r="E2" t="n">
-        <v>9.156656102141225</v>
+        <v>1.487956616597949</v>
       </c>
       <c r="F2" t="n">
-        <v>9.148679235054622</v>
+        <v>1.486660375696376</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.62923541392249</v>
+        <v>6.602250754762405</v>
       </c>
       <c r="D3" t="n">
-        <v>40.58279929504639</v>
+        <v>6.594704885445037</v>
       </c>
       <c r="E3" t="n">
-        <v>9.156656102141225</v>
+        <v>1.487956616597949</v>
       </c>
       <c r="F3" t="n">
-        <v>9.148679235054622</v>
+        <v>1.486660375696376</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.43350520932546</v>
+        <v>6.732944596515387</v>
       </c>
       <c r="D4" t="n">
-        <v>41.38939068331803</v>
+        <v>6.72577598603918</v>
       </c>
       <c r="E4" t="n">
-        <v>9.156656102141225</v>
+        <v>1.487956616597949</v>
       </c>
       <c r="F4" t="n">
-        <v>9.148679235054622</v>
+        <v>1.486660375696376</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.47238531910953</v>
+        <v>6.739262614355299</v>
       </c>
       <c r="D5" t="n">
-        <v>41.43185321053511</v>
+        <v>6.732676146711955</v>
       </c>
       <c r="E5" t="n">
-        <v>9.156656102141225</v>
+        <v>1.487956616597949</v>
       </c>
       <c r="F5" t="n">
-        <v>9.148679235054622</v>
+        <v>1.486660375696376</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.89264877186569</v>
+        <v>4.045055425428174</v>
       </c>
       <c r="D6" t="n">
-        <v>24.8586809009357</v>
+        <v>4.039535646402052</v>
       </c>
       <c r="E6" t="n">
-        <v>9.156656102141225</v>
+        <v>1.487956616597949</v>
       </c>
       <c r="F6" t="n">
-        <v>9.148679235054622</v>
+        <v>1.486660375696376</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.89969412746348</v>
+        <v>6.158700295712817</v>
       </c>
       <c r="D7" t="n">
-        <v>37.8650716610458</v>
+        <v>6.153074144919942</v>
       </c>
       <c r="E7" t="n">
-        <v>9.156656102141225</v>
+        <v>1.487956616597949</v>
       </c>
       <c r="F7" t="n">
-        <v>9.148679235054622</v>
+        <v>1.486660375696376</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>19.08969360252107</v>
+        <v>3.102075210409675</v>
       </c>
       <c r="D8" t="n">
-        <v>19.0420125821146</v>
+        <v>3.094327044593622</v>
       </c>
       <c r="E8" t="n">
-        <v>9.156656102141225</v>
+        <v>1.487956616597949</v>
       </c>
       <c r="F8" t="n">
-        <v>9.148679235054622</v>
+        <v>1.486660375696376</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.34764578683227</v>
+        <v>3.793992440360245</v>
       </c>
       <c r="D9" t="n">
-        <v>23.3378028949642</v>
+        <v>3.792392970431683</v>
       </c>
       <c r="E9" t="n">
-        <v>9.156656102141225</v>
+        <v>1.487956616597949</v>
       </c>
       <c r="F9" t="n">
-        <v>9.148679235054622</v>
+        <v>1.486660375696376</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>33.2199685015465</v>
+        <v>5.398244881501306</v>
       </c>
       <c r="D10" t="n">
-        <v>33.20908008731649</v>
+        <v>5.39647551418893</v>
       </c>
       <c r="E10" t="n">
-        <v>9.156656102141225</v>
+        <v>1.487956616597949</v>
       </c>
       <c r="F10" t="n">
-        <v>9.148679235054622</v>
+        <v>1.486660375696376</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>19.18334903437543</v>
+        <v>3.117294218086007</v>
       </c>
       <c r="D11" t="n">
-        <v>19.18542312193923</v>
+        <v>3.117631257315125</v>
       </c>
       <c r="E11" t="n">
-        <v>9.156656102141225</v>
+        <v>1.487956616597949</v>
       </c>
       <c r="F11" t="n">
-        <v>9.148679235054622</v>
+        <v>1.486660375696376</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>34.36972196207024</v>
+        <v>5.585079818836415</v>
       </c>
       <c r="D12" t="n">
-        <v>34.37394953943117</v>
+        <v>5.585766800157566</v>
       </c>
       <c r="E12" t="n">
-        <v>9.156656102141225</v>
+        <v>1.487956616597949</v>
       </c>
       <c r="F12" t="n">
-        <v>9.148679235054622</v>
+        <v>1.486660375696376</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>17.0268193602747</v>
+        <v>2.766858146044638</v>
       </c>
       <c r="D13" t="n">
-        <v>17.06980390075568</v>
+        <v>2.773843133872799</v>
       </c>
       <c r="E13" t="n">
-        <v>9.156656102141225</v>
+        <v>1.487956616597949</v>
       </c>
       <c r="F13" t="n">
-        <v>9.148679235054622</v>
+        <v>1.486660375696376</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>25.97229059972053</v>
+        <v>4.220497222454587</v>
       </c>
       <c r="D14" t="n">
-        <v>26.00803844285112</v>
+        <v>4.226306246963307</v>
       </c>
       <c r="E14" t="n">
-        <v>9.156656102141225</v>
+        <v>1.487956616597949</v>
       </c>
       <c r="F14" t="n">
-        <v>9.148679235054622</v>
+        <v>1.486660375696376</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>43.77107925574683</v>
+        <v>7.11280037905886</v>
       </c>
       <c r="D15" t="n">
-        <v>43.81188980838957</v>
+        <v>7.119432093863304</v>
       </c>
       <c r="E15" t="n">
-        <v>9.156656102141225</v>
+        <v>1.487956616597949</v>
       </c>
       <c r="F15" t="n">
-        <v>9.148679235054622</v>
+        <v>1.486660375696376</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>36.34681733536722</v>
+        <v>5.906357816997174</v>
       </c>
       <c r="D16" t="n">
-        <v>36.39465257213337</v>
+        <v>5.914131042971674</v>
       </c>
       <c r="E16" t="n">
-        <v>9.156656102141225</v>
+        <v>1.487956616597949</v>
       </c>
       <c r="F16" t="n">
-        <v>9.148679235054622</v>
+        <v>1.486660375696376</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
